--- a/VanHanhCD1/wwwroot/templates/BMVH_QG2ThieuKet1.xlsx
+++ b/VanHanhCD1/wwwroot/templates/BMVH_QG2ThieuKet1.xlsx
@@ -5,21 +5,30 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\03. Project Hoa Phat\07. Backend\VanHanhCD1_API-main\VanHanhCD1\wwwroot\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\02. Du An Hoa Phat\API\VanHanhCD1_API-release\VanHanhCD1\wwwroot\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C7A00D-E359-4FAB-9C6B-8ADB03816E89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B0BBDD-36C0-4ECA-8E11-FB3FADD95178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{749D0495-9471-4B75-B577-F5813F33161C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{749D0495-9471-4B75-B577-F5813F33161C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -871,13 +880,57 @@
     <xf numFmtId="164" fontId="18" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -899,14 +952,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -918,68 +967,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1002,6 +996,21 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1560,7 +1569,7 @@
   <dimension ref="A1:Z35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" customWidth="1"/>
     <col min="2" max="2" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.85546875" bestFit="1" customWidth="1"/>
@@ -1574,190 +1583,190 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="37"/>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="S1" s="38" t="s">
-        <v>0</v>
-      </c>
-      <c r="T1" s="39"/>
-      <c r="U1" s="39"/>
-      <c r="V1" s="39"/>
-      <c r="W1" s="39"/>
-      <c r="X1" s="39"/>
-      <c r="Y1" s="39"/>
-      <c r="Z1" s="39"/>
+      <c r="A1" s="14"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="S1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="16"/>
+      <c r="Y1" s="16"/>
+      <c r="Z1" s="16"/>
     </row>
     <row r="2" spans="1:26" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="41"/>
-      <c r="S2" s="41"/>
-      <c r="T2" s="41"/>
-      <c r="U2" s="41"/>
-      <c r="V2" s="41"/>
-      <c r="W2" s="41"/>
-      <c r="X2" s="41"/>
-      <c r="Y2" s="41"/>
-      <c r="Z2" s="41"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="18"/>
+      <c r="P2" s="18"/>
+      <c r="Q2" s="18"/>
+      <c r="R2" s="18"/>
+      <c r="S2" s="18"/>
+      <c r="T2" s="18"/>
+      <c r="U2" s="18"/>
+      <c r="V2" s="18"/>
+      <c r="W2" s="18"/>
+      <c r="X2" s="18"/>
+      <c r="Y2" s="18"/>
+      <c r="Z2" s="18"/>
     </row>
     <row r="3" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
-      <c r="S3" s="24"/>
-      <c r="T3" s="24"/>
-      <c r="U3" s="24"/>
-      <c r="V3" s="24"/>
-      <c r="W3" s="24"/>
-      <c r="X3" s="24"/>
-      <c r="Y3" s="24"/>
-      <c r="Z3" s="24"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20"/>
+      <c r="R3" s="20"/>
+      <c r="S3" s="20"/>
+      <c r="T3" s="20"/>
+      <c r="U3" s="20"/>
+      <c r="V3" s="20"/>
+      <c r="W3" s="20"/>
+      <c r="X3" s="20"/>
+      <c r="Y3" s="20"/>
+      <c r="Z3" s="20"/>
     </row>
     <row r="4" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="36" t="s">
+      <c r="D4" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="G4" s="36" t="s">
+      <c r="G4" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="16" t="s">
+      <c r="J4" s="25"/>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+      <c r="M4" s="25"/>
+      <c r="N4" s="25"/>
+      <c r="O4" s="25"/>
+      <c r="P4" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="16"/>
-      <c r="S4" s="16"/>
-      <c r="T4" s="16"/>
-      <c r="U4" s="16"/>
-      <c r="V4" s="16"/>
-      <c r="W4" s="16"/>
-      <c r="X4" s="16" t="s">
+      <c r="Q4" s="24"/>
+      <c r="R4" s="24"/>
+      <c r="S4" s="24"/>
+      <c r="T4" s="24"/>
+      <c r="U4" s="24"/>
+      <c r="V4" s="24"/>
+      <c r="W4" s="24"/>
+      <c r="X4" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="Y4" s="16"/>
-      <c r="Z4" s="16"/>
+      <c r="Y4" s="24"/>
+      <c r="Z4" s="24"/>
     </row>
     <row r="5" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="43"/>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="36"/>
-      <c r="I5" s="14" t="s">
+      <c r="A5" s="22"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14" t="s">
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14" t="s">
+      <c r="M5" s="25"/>
+      <c r="N5" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="O5" s="14"/>
-      <c r="P5" s="16" t="s">
+      <c r="O5" s="25"/>
+      <c r="P5" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="16" t="s">
+      <c r="Q5" s="24"/>
+      <c r="R5" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="S5" s="16"/>
-      <c r="T5" s="16" t="s">
+      <c r="S5" s="24"/>
+      <c r="T5" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="U5" s="16"/>
-      <c r="V5" s="16" t="s">
+      <c r="U5" s="24"/>
+      <c r="V5" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="W5" s="16"/>
-      <c r="X5" s="27" t="s">
+      <c r="W5" s="24"/>
+      <c r="X5" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="Y5" s="27" t="s">
+      <c r="Y5" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="Z5" s="27" t="s">
+      <c r="Z5" s="26" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="44"/>
-      <c r="B6" s="36"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
+      <c r="A6" s="23"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
       <c r="I6" s="1" t="s">
         <v>4</v>
       </c>
@@ -1803,12 +1812,12 @@
       <c r="W6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="X6" s="27"/>
-      <c r="Y6" s="27"/>
-      <c r="Z6" s="27"/>
+      <c r="X6" s="26"/>
+      <c r="Y6" s="26"/>
+      <c r="Z6" s="26"/>
     </row>
     <row r="7" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="35"/>
+      <c r="A7" s="31"/>
       <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
@@ -1910,7 +1919,7 @@
       </c>
     </row>
     <row r="8" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="31"/>
+      <c r="A8" s="27"/>
       <c r="B8" s="3" t="s">
         <v>20</v>
       </c>
@@ -2012,7 +2021,7 @@
       </c>
     </row>
     <row r="9" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
+      <c r="A9" s="27"/>
       <c r="B9" s="3" t="s">
         <v>21</v>
       </c>
@@ -2114,7 +2123,7 @@
       </c>
     </row>
     <row r="10" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="31"/>
+      <c r="A10" s="27"/>
       <c r="B10" s="3" t="s">
         <v>22</v>
       </c>
@@ -2216,7 +2225,7 @@
       </c>
     </row>
     <row r="11" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
+      <c r="A11" s="27"/>
       <c r="B11" s="3" t="s">
         <v>23</v>
       </c>
@@ -2318,7 +2327,7 @@
       </c>
     </row>
     <row r="12" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="31"/>
+      <c r="A12" s="27"/>
       <c r="B12" s="3" t="s">
         <v>24</v>
       </c>
@@ -2420,7 +2429,7 @@
       </c>
     </row>
     <row r="13" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="31"/>
+      <c r="A13" s="27"/>
       <c r="B13" s="3" t="s">
         <v>25</v>
       </c>
@@ -2522,7 +2531,7 @@
       </c>
     </row>
     <row r="14" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="31"/>
+      <c r="A14" s="27"/>
       <c r="B14" s="3" t="s">
         <v>26</v>
       </c>
@@ -2624,7 +2633,7 @@
       </c>
     </row>
     <row r="15" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="31"/>
+      <c r="A15" s="27"/>
       <c r="B15" s="3" t="s">
         <v>27</v>
       </c>
@@ -2726,7 +2735,7 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="31"/>
+      <c r="A16" s="27"/>
       <c r="B16" s="5" t="s">
         <v>28</v>
       </c>
@@ -2828,7 +2837,7 @@
       </c>
     </row>
     <row r="17" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="31"/>
+      <c r="A17" s="27"/>
       <c r="B17" s="5" t="s">
         <v>29</v>
       </c>
@@ -2930,7 +2939,7 @@
       </c>
     </row>
     <row r="18" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="31"/>
+      <c r="A18" s="27"/>
       <c r="B18" s="5" t="s">
         <v>30</v>
       </c>
@@ -3032,7 +3041,7 @@
       </c>
     </row>
     <row r="19" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="31"/>
+      <c r="A19" s="27"/>
       <c r="B19" s="5" t="s">
         <v>31</v>
       </c>
@@ -3134,7 +3143,7 @@
       </c>
     </row>
     <row r="20" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="31"/>
+      <c r="A20" s="27"/>
       <c r="B20" s="5" t="s">
         <v>32</v>
       </c>
@@ -3236,7 +3245,7 @@
       </c>
     </row>
     <row r="21" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="31"/>
+      <c r="A21" s="27"/>
       <c r="B21" s="5" t="s">
         <v>33</v>
       </c>
@@ -3338,7 +3347,7 @@
       </c>
     </row>
     <row r="22" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="31"/>
+      <c r="A22" s="27"/>
       <c r="B22" s="5" t="s">
         <v>34</v>
       </c>
@@ -3440,7 +3449,7 @@
       </c>
     </row>
     <row r="23" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="31"/>
+      <c r="A23" s="27"/>
       <c r="B23" s="5" t="s">
         <v>35</v>
       </c>
@@ -3542,7 +3551,7 @@
       </c>
     </row>
     <row r="24" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="31"/>
+      <c r="A24" s="27"/>
       <c r="B24" s="5" t="s">
         <v>36</v>
       </c>
@@ -3644,7 +3653,7 @@
       </c>
     </row>
     <row r="25" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="31"/>
+      <c r="A25" s="27"/>
       <c r="B25" s="5" t="s">
         <v>37</v>
       </c>
@@ -3746,7 +3755,7 @@
       </c>
     </row>
     <row r="26" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="31"/>
+      <c r="A26" s="27"/>
       <c r="B26" s="5" t="s">
         <v>38</v>
       </c>
@@ -3848,7 +3857,7 @@
       </c>
     </row>
     <row r="27" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="31"/>
+      <c r="A27" s="27"/>
       <c r="B27" s="5" t="s">
         <v>39</v>
       </c>
@@ -3950,7 +3959,7 @@
       </c>
     </row>
     <row r="28" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="31"/>
+      <c r="A28" s="27"/>
       <c r="B28" s="5" t="s">
         <v>40</v>
       </c>
@@ -4052,7 +4061,7 @@
       </c>
     </row>
     <row r="29" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="31"/>
+      <c r="A29" s="27"/>
       <c r="B29" s="5" t="s">
         <v>41</v>
       </c>
@@ -4154,7 +4163,7 @@
       </c>
     </row>
     <row r="30" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="32"/>
+      <c r="A30" s="28"/>
       <c r="B30" s="5" t="s">
         <v>42</v>
       </c>
@@ -4256,173 +4265,200 @@
       </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A31" s="33" t="s">
+      <c r="A31" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="34"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="34"/>
-      <c r="I31" s="34"/>
-      <c r="J31" s="34"/>
-      <c r="K31" s="34"/>
-      <c r="L31" s="34"/>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
-      <c r="O31" s="34"/>
-      <c r="P31" s="34"/>
-      <c r="Q31" s="34"/>
-      <c r="R31" s="34"/>
-      <c r="S31" s="34"/>
-      <c r="T31" s="34"/>
-      <c r="U31" s="34"/>
-      <c r="V31" s="34"/>
-      <c r="W31" s="34"/>
-      <c r="X31" s="34"/>
-      <c r="Y31" s="34"/>
-      <c r="Z31" s="34"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="30"/>
+      <c r="O31" s="30"/>
+      <c r="P31" s="30"/>
+      <c r="Q31" s="30"/>
+      <c r="R31" s="30"/>
+      <c r="S31" s="30"/>
+      <c r="T31" s="30"/>
+      <c r="U31" s="30"/>
+      <c r="V31" s="30"/>
+      <c r="W31" s="30"/>
+      <c r="X31" s="30"/>
+      <c r="Y31" s="30"/>
+      <c r="Z31" s="30"/>
     </row>
     <row r="32" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A32" s="25" t="s">
+      <c r="A32" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="26"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="15" t="s">
+      <c r="B32" s="41"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="16"/>
-      <c r="J32" s="15" t="s">
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="K32" s="17"/>
-      <c r="L32" s="17"/>
-      <c r="M32" s="17"/>
-      <c r="N32" s="17"/>
-      <c r="O32" s="16"/>
-      <c r="P32" s="25" t="s">
+      <c r="K32" s="33"/>
+      <c r="L32" s="33"/>
+      <c r="M32" s="33"/>
+      <c r="N32" s="33"/>
+      <c r="O32" s="24"/>
+      <c r="P32" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="Q32" s="26"/>
-      <c r="R32" s="27"/>
-      <c r="S32" s="15" t="s">
+      <c r="Q32" s="41"/>
+      <c r="R32" s="26"/>
+      <c r="S32" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="T32" s="17"/>
-      <c r="U32" s="17"/>
-      <c r="V32" s="17"/>
-      <c r="W32" s="17"/>
-      <c r="X32" s="14" t="s">
+      <c r="T32" s="33"/>
+      <c r="U32" s="33"/>
+      <c r="V32" s="33"/>
+      <c r="W32" s="33"/>
+      <c r="X32" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="Y32" s="14"/>
-      <c r="Z32" s="14"/>
+      <c r="Y32" s="25"/>
+      <c r="Z32" s="25"/>
     </row>
     <row r="33" spans="1:26" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A33" s="28"/>
-      <c r="B33" s="29"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="15" t="s">
+      <c r="A33" s="42"/>
+      <c r="B33" s="43"/>
+      <c r="C33" s="44"/>
+      <c r="D33" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="E33" s="16"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="16"/>
-      <c r="J33" s="15" t="s">
+      <c r="E33" s="24"/>
+      <c r="F33" s="32"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="20"/>
-      <c r="M33" s="21"/>
-      <c r="N33" s="21"/>
-      <c r="O33" s="22"/>
-      <c r="P33" s="28"/>
-      <c r="Q33" s="29"/>
-      <c r="R33" s="30"/>
-      <c r="S33" s="15" t="s">
+      <c r="K33" s="24"/>
+      <c r="L33" s="36"/>
+      <c r="M33" s="37"/>
+      <c r="N33" s="37"/>
+      <c r="O33" s="38"/>
+      <c r="P33" s="42"/>
+      <c r="Q33" s="43"/>
+      <c r="R33" s="44"/>
+      <c r="S33" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="T33" s="16"/>
-      <c r="U33" s="20"/>
-      <c r="V33" s="21"/>
-      <c r="W33" s="22"/>
+      <c r="T33" s="24"/>
+      <c r="U33" s="36"/>
+      <c r="V33" s="37"/>
+      <c r="W33" s="38"/>
       <c r="X33" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="Y33" s="20"/>
-      <c r="Z33" s="22"/>
+      <c r="Y33" s="36"/>
+      <c r="Z33" s="38"/>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A34" s="23" t="s">
+      <c r="A34" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="B34" s="24"/>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
-      <c r="F34" s="24"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="24"/>
-      <c r="I34" s="24"/>
-      <c r="J34" s="24"/>
-      <c r="K34" s="24"/>
-      <c r="L34" s="24"/>
-      <c r="M34" s="24"/>
-      <c r="N34" s="24"/>
-      <c r="O34" s="24"/>
-      <c r="P34" s="24"/>
-      <c r="Q34" s="24"/>
-      <c r="R34" s="24"/>
-      <c r="S34" s="24"/>
-      <c r="T34" s="24"/>
-      <c r="U34" s="24"/>
-      <c r="V34" s="24"/>
-      <c r="W34" s="24"/>
-      <c r="X34" s="24"/>
-      <c r="Y34" s="24"/>
-      <c r="Z34" s="24"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="20"/>
+      <c r="M34" s="20"/>
+      <c r="N34" s="20"/>
+      <c r="O34" s="20"/>
+      <c r="P34" s="20"/>
+      <c r="Q34" s="20"/>
+      <c r="R34" s="20"/>
+      <c r="S34" s="20"/>
+      <c r="T34" s="20"/>
+      <c r="U34" s="20"/>
+      <c r="V34" s="20"/>
+      <c r="W34" s="20"/>
+      <c r="X34" s="20"/>
+      <c r="Y34" s="20"/>
+      <c r="Z34" s="20"/>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="19"/>
-      <c r="J35" s="19"/>
-      <c r="K35" s="19"/>
-      <c r="L35" s="19"/>
-      <c r="M35" s="19"/>
-      <c r="N35" s="19"/>
-      <c r="O35" s="19"/>
-      <c r="P35" s="19"/>
-      <c r="Q35" s="19"/>
-      <c r="R35" s="19"/>
-      <c r="S35" s="19"/>
-      <c r="T35" s="19"/>
-      <c r="U35" s="19"/>
-      <c r="V35" s="19"/>
-      <c r="W35" s="19"/>
-      <c r="X35" s="19"/>
-      <c r="Y35" s="19"/>
-      <c r="Z35" s="19"/>
+      <c r="B35" s="35"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="35"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="35"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="35"/>
+      <c r="J35" s="35"/>
+      <c r="K35" s="35"/>
+      <c r="L35" s="35"/>
+      <c r="M35" s="35"/>
+      <c r="N35" s="35"/>
+      <c r="O35" s="35"/>
+      <c r="P35" s="35"/>
+      <c r="Q35" s="35"/>
+      <c r="R35" s="35"/>
+      <c r="S35" s="35"/>
+      <c r="T35" s="35"/>
+      <c r="U35" s="35"/>
+      <c r="V35" s="35"/>
+      <c r="W35" s="35"/>
+      <c r="X35" s="35"/>
+      <c r="Y35" s="35"/>
+      <c r="Z35" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="X32:Z32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:I33"/>
+    <mergeCell ref="A35:Z35"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="L33:O33"/>
+    <mergeCell ref="S33:T33"/>
+    <mergeCell ref="U33:W33"/>
+    <mergeCell ref="Y33:Z33"/>
+    <mergeCell ref="A34:Z34"/>
+    <mergeCell ref="A32:C33"/>
+    <mergeCell ref="D32:I32"/>
+    <mergeCell ref="J32:O32"/>
+    <mergeCell ref="P32:R33"/>
+    <mergeCell ref="S32:W32"/>
+    <mergeCell ref="X5:X6"/>
+    <mergeCell ref="Y5:Y6"/>
+    <mergeCell ref="Z5:Z6"/>
+    <mergeCell ref="A19:A30"/>
+    <mergeCell ref="A31:Z31"/>
+    <mergeCell ref="A7:A18"/>
+    <mergeCell ref="G4:G6"/>
+    <mergeCell ref="H4:H6"/>
+    <mergeCell ref="I4:O4"/>
+    <mergeCell ref="P4:W4"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="V5:W5"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="S1:Z1"/>
     <mergeCell ref="A2:Z2"/>
@@ -4439,33 +4475,6 @@
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="P5:Q5"/>
     <mergeCell ref="R5:S5"/>
-    <mergeCell ref="X5:X6"/>
-    <mergeCell ref="Y5:Y6"/>
-    <mergeCell ref="Z5:Z6"/>
-    <mergeCell ref="A19:A30"/>
-    <mergeCell ref="A31:Z31"/>
-    <mergeCell ref="A7:A18"/>
-    <mergeCell ref="G4:G6"/>
-    <mergeCell ref="H4:H6"/>
-    <mergeCell ref="I4:O4"/>
-    <mergeCell ref="P4:W4"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="V5:W5"/>
-    <mergeCell ref="X32:Z32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:I33"/>
-    <mergeCell ref="A35:Z35"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="L33:O33"/>
-    <mergeCell ref="S33:T33"/>
-    <mergeCell ref="U33:W33"/>
-    <mergeCell ref="Y33:Z33"/>
-    <mergeCell ref="A34:Z34"/>
-    <mergeCell ref="A32:C33"/>
-    <mergeCell ref="D32:I32"/>
-    <mergeCell ref="J32:O32"/>
-    <mergeCell ref="P32:R33"/>
-    <mergeCell ref="S32:W32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4484,10 +4493,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A1" s="53"/>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
+      <c r="A1" s="48"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
@@ -4502,60 +4511,60 @@
       <c r="P1" s="7"/>
       <c r="Q1" s="7"/>
       <c r="R1" s="7"/>
-      <c r="S1" s="54" t="s">
+      <c r="S1" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="T1" s="54"/>
-      <c r="U1" s="54"/>
-      <c r="V1" s="54"/>
+      <c r="T1" s="49"/>
+      <c r="U1" s="49"/>
+      <c r="V1" s="49"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="53"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
+      <c r="A2" s="48"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
       <c r="E2" s="7"/>
-      <c r="F2" s="55" t="s">
+      <c r="F2" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
-      <c r="Q2" s="55"/>
-      <c r="R2" s="55"/>
-      <c r="S2" s="56" t="s">
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="50"/>
+      <c r="P2" s="50"/>
+      <c r="Q2" s="50"/>
+      <c r="R2" s="50"/>
+      <c r="S2" s="51" t="s">
         <v>71</v>
       </c>
-      <c r="T2" s="56"/>
-      <c r="U2" s="56"/>
-      <c r="V2" s="56"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="51"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A3" s="53"/>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
+      <c r="A3" s="48"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
       <c r="E3" s="7"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="55"/>
-      <c r="L3" s="55"/>
-      <c r="M3" s="55"/>
-      <c r="N3" s="55"/>
-      <c r="O3" s="55"/>
-      <c r="P3" s="55"/>
-      <c r="Q3" s="55"/>
-      <c r="R3" s="55"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="50"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="50"/>
+      <c r="M3" s="50"/>
+      <c r="N3" s="50"/>
+      <c r="O3" s="50"/>
+      <c r="P3" s="50"/>
+      <c r="Q3" s="50"/>
+      <c r="R3" s="50"/>
       <c r="S3" s="7"/>
       <c r="T3" s="7"/>
       <c r="U3" s="7"/>
@@ -4588,11 +4597,11 @@
       <c r="V4" s="9"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A5" s="57" t="s">
+      <c r="A5" s="52" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="58"/>
-      <c r="C5" s="59"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="54"/>
       <c r="D5" s="10" t="s">
         <v>74</v>
       </c>
@@ -4670,11 +4679,11 @@
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="B6" s="52"/>
-      <c r="C6" s="49"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="47"/>
       <c r="D6" s="12" t="s">
         <v>79</v>
       </c>
@@ -4706,11 +4715,11 @@
       <c r="AB6" s="11"/>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="45" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="52"/>
-      <c r="C7" s="49"/>
+      <c r="B7" s="46"/>
+      <c r="C7" s="47"/>
       <c r="D7" s="12" t="s">
         <v>80</v>
       </c>
@@ -4740,11 +4749,11 @@
       <c r="AB7" s="11"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="21"/>
-      <c r="C8" s="22"/>
+      <c r="B8" s="37"/>
+      <c r="C8" s="38"/>
       <c r="D8" s="12" t="s">
         <v>81</v>
       </c>
@@ -4774,11 +4783,11 @@
       <c r="AB8" s="11"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="22"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="38"/>
       <c r="D9" s="12" t="s">
         <v>82</v>
       </c>
@@ -4808,11 +4817,11 @@
       <c r="AB9" s="11"/>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="22"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="38"/>
       <c r="D10" s="12" t="s">
         <v>83</v>
       </c>
@@ -4842,11 +4851,11 @@
       <c r="AB10" s="11"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="21"/>
-      <c r="C11" s="22"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="38"/>
       <c r="D11" s="12" t="s">
         <v>84</v>
       </c>
@@ -4876,10 +4885,10 @@
       <c r="AB11" s="11"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="55" t="s">
         <v>77</v>
       </c>
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="55" t="s">
         <v>58</v>
       </c>
       <c r="C12" s="11" t="s">
@@ -4914,8 +4923,8 @@
       <c r="AB12" s="11"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A13" s="47"/>
-      <c r="B13" s="47"/>
+      <c r="A13" s="56"/>
+      <c r="B13" s="56"/>
       <c r="C13" s="11" t="s">
         <v>5</v>
       </c>
@@ -4948,8 +4957,8 @@
       <c r="AB13" s="11"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A14" s="47"/>
-      <c r="B14" s="46"/>
+      <c r="A14" s="56"/>
+      <c r="B14" s="57"/>
       <c r="C14" s="11" t="s">
         <v>6</v>
       </c>
@@ -4982,8 +4991,8 @@
       <c r="AB14" s="11"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A15" s="47"/>
-      <c r="B15" s="45" t="s">
+      <c r="A15" s="56"/>
+      <c r="B15" s="55" t="s">
         <v>59</v>
       </c>
       <c r="C15" s="11" t="s">
@@ -5018,8 +5027,8 @@
       <c r="AB15" s="11"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A16" s="47"/>
-      <c r="B16" s="46"/>
+      <c r="A16" s="56"/>
+      <c r="B16" s="57"/>
       <c r="C16" s="11" t="s">
         <v>8</v>
       </c>
@@ -5052,8 +5061,8 @@
       <c r="AB16" s="11"/>
     </row>
     <row r="17" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A17" s="47"/>
-      <c r="B17" s="45" t="s">
+      <c r="A17" s="56"/>
+      <c r="B17" s="55" t="s">
         <v>60</v>
       </c>
       <c r="C17" s="11" t="s">
@@ -5088,8 +5097,8 @@
       <c r="AB17" s="11"/>
     </row>
     <row r="18" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A18" s="46"/>
-      <c r="B18" s="46"/>
+      <c r="A18" s="57"/>
+      <c r="B18" s="57"/>
       <c r="C18" s="11" t="s">
         <v>10</v>
       </c>
@@ -5122,10 +5131,10 @@
       <c r="AB18" s="11"/>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A19" s="45" t="s">
+      <c r="A19" s="55" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="45" t="s">
+      <c r="B19" s="55" t="s">
         <v>62</v>
       </c>
       <c r="C19" s="11" t="s">
@@ -5160,8 +5169,8 @@
       <c r="AB19" s="11"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A20" s="47"/>
-      <c r="B20" s="46"/>
+      <c r="A20" s="56"/>
+      <c r="B20" s="57"/>
       <c r="C20" s="11" t="s">
         <v>12</v>
       </c>
@@ -5194,8 +5203,8 @@
       <c r="AB20" s="11"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A21" s="47"/>
-      <c r="B21" s="45" t="s">
+      <c r="A21" s="56"/>
+      <c r="B21" s="55" t="s">
         <v>63</v>
       </c>
       <c r="C21" s="11" t="s">
@@ -5230,8 +5239,8 @@
       <c r="AB21" s="11"/>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A22" s="47"/>
-      <c r="B22" s="46"/>
+      <c r="A22" s="56"/>
+      <c r="B22" s="57"/>
       <c r="C22" s="11" t="s">
         <v>14</v>
       </c>
@@ -5264,8 +5273,8 @@
       <c r="AB22" s="11"/>
     </row>
     <row r="23" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A23" s="47"/>
-      <c r="B23" s="45" t="s">
+      <c r="A23" s="56"/>
+      <c r="B23" s="55" t="s">
         <v>64</v>
       </c>
       <c r="C23" s="11" t="s">
@@ -5300,8 +5309,8 @@
       <c r="AB23" s="11"/>
     </row>
     <row r="24" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A24" s="47"/>
-      <c r="B24" s="46"/>
+      <c r="A24" s="56"/>
+      <c r="B24" s="57"/>
       <c r="C24" s="11" t="s">
         <v>16</v>
       </c>
@@ -5334,8 +5343,8 @@
       <c r="AB24" s="11"/>
     </row>
     <row r="25" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A25" s="47"/>
-      <c r="B25" s="45" t="s">
+      <c r="A25" s="56"/>
+      <c r="B25" s="55" t="s">
         <v>65</v>
       </c>
       <c r="C25" s="11" t="s">
@@ -5370,8 +5379,8 @@
       <c r="AB25" s="11"/>
     </row>
     <row r="26" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A26" s="46"/>
-      <c r="B26" s="46"/>
+      <c r="A26" s="57"/>
+      <c r="B26" s="57"/>
       <c r="C26" s="11" t="s">
         <v>18</v>
       </c>
@@ -5404,13 +5413,13 @@
       <c r="AB26" s="11"/>
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A27" s="45" t="s">
+      <c r="A27" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="B27" s="48" t="s">
+      <c r="B27" s="45" t="s">
         <v>67</v>
       </c>
-      <c r="C27" s="49"/>
+      <c r="C27" s="47"/>
       <c r="D27" s="12" t="s">
         <v>99</v>
       </c>
@@ -5440,11 +5449,11 @@
       <c r="AB27" s="11"/>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A28" s="47"/>
-      <c r="B28" s="20" t="s">
+      <c r="A28" s="56"/>
+      <c r="B28" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="C28" s="22"/>
+      <c r="C28" s="38"/>
       <c r="D28" s="12" t="s">
         <v>100</v>
       </c>
@@ -5474,11 +5483,11 @@
       <c r="AB28" s="11"/>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A29" s="46"/>
-      <c r="B29" s="50" t="s">
+      <c r="A29" s="57"/>
+      <c r="B29" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="51"/>
+      <c r="C29" s="59"/>
       <c r="D29" s="12" t="s">
         <v>101</v>
       </c>
@@ -5509,12 +5518,15 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A1:D3"/>
-    <mergeCell ref="S1:V1"/>
-    <mergeCell ref="F2:R3"/>
-    <mergeCell ref="S2:V2"/>
-    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A11:C11"/>
     <mergeCell ref="A12:A18"/>
     <mergeCell ref="B12:B14"/>
     <mergeCell ref="B15:B16"/>
@@ -5522,17 +5534,14 @@
     <mergeCell ref="A19:A26"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="B21:B22"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A11:C11"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="B25:B26"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A1:D3"/>
+    <mergeCell ref="S1:V1"/>
+    <mergeCell ref="F2:R3"/>
+    <mergeCell ref="S2:V2"/>
+    <mergeCell ref="A5:C5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
